--- a/diseases/d099/1995-1999.xlsx
+++ b/diseases/d099/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>27</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>10</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>21</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>8</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>14</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>20</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>27</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>9</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>26</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>17</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>20</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>14</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>15</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>19</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>35</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>27</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>22</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>31</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>24</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>15</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>29</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>15</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>22</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>16</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>17</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>16</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>24</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>13</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>40</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>12</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>29</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>16</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>27</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>9</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>10</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>15</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>18</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>15</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>18</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>18</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>12</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>19</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>21</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>31</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>16</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>26</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18843,9 +18705,6 @@
       <c r="O94" t="n">
         <v>29</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19236,9 +19095,6 @@
       <c r="O96" t="n">
         <v>13</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19629,9 +19485,6 @@
       <c r="O98" t="n">
         <v>26</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20261,9 +20114,6 @@
       <c r="O101" t="n">
         <v>17</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="S101" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20654,9 +20504,6 @@
       <c r="O103" t="n">
         <v>18</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="S103" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21047,9 +20894,6 @@
       <c r="O105" t="n">
         <v>14</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="S105" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21440,9 +21284,6 @@
       <c r="O107" t="n">
         <v>18</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="S107" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21833,9 +21674,6 @@
       <c r="O109" t="n">
         <v>15</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="S109" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22226,9 +22064,6 @@
       <c r="O111" t="n">
         <v>37</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="S111" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22619,9 +22454,6 @@
       <c r="O113" t="n">
         <v>24</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="S113" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23012,9 +22844,6 @@
       <c r="O115" t="n">
         <v>22</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="S115" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23405,9 +23234,6 @@
       <c r="O117" t="n">
         <v>14</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="S117" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23798,9 +23624,6 @@
       <c r="O119" t="n">
         <v>26</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="S119" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24191,9 +24014,6 @@
       <c r="O121" t="n">
         <v>19</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="S121" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24584,9 +24404,6 @@
       <c r="O123" t="n">
         <v>34</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24977,9 +24794,6 @@
       <c r="O125" t="n">
         <v>8</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="S125" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25370,9 +25184,6 @@
       <c r="O127" t="n">
         <v>37</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="S127" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25763,9 +25574,6 @@
       <c r="O129" t="n">
         <v>32</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="S129" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26156,9 +25964,6 @@
       <c r="O131" t="n">
         <v>44</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="S131" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26549,9 +26354,6 @@
       <c r="O133" t="n">
         <v>29</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="S133" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26942,9 +26744,6 @@
       <c r="O135" t="n">
         <v>28</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="S135" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27335,9 +27134,6 @@
       <c r="O137" t="n">
         <v>46</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27728,9 +27524,6 @@
       <c r="O139" t="n">
         <v>27</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="S139" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28121,9 +27914,6 @@
       <c r="O141" t="n">
         <v>32</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="S141" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28514,9 +28304,6 @@
       <c r="O143" t="n">
         <v>16</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28907,9 +28694,6 @@
       <c r="O145" t="n">
         <v>33</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="S145" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29300,9 +29084,6 @@
       <c r="O147" t="n">
         <v>21</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="S147" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29932,9 +29713,6 @@
       <c r="O150" t="n">
         <v>28</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30325,9 +30103,6 @@
       <c r="O152" t="n">
         <v>17</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30718,9 +30493,6 @@
       <c r="O154" t="n">
         <v>22</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="S154" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31111,9 +30883,6 @@
       <c r="O156" t="n">
         <v>23</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="S156" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31504,9 +31273,6 @@
       <c r="O158" t="n">
         <v>35</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31897,9 +31663,6 @@
       <c r="O160" t="n">
         <v>10</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32290,9 +32053,6 @@
       <c r="O162" t="n">
         <v>28</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="S162" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32683,9 +32443,6 @@
       <c r="O164" t="n">
         <v>21</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="S164" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33076,9 +32833,6 @@
       <c r="O166" t="n">
         <v>30</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="S166" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33469,9 +33223,6 @@
       <c r="O168" t="n">
         <v>47</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="S168" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33862,9 +33613,6 @@
       <c r="O170" t="n">
         <v>25</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34255,9 +34003,6 @@
       <c r="O172" t="n">
         <v>29</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="S172" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34648,9 +34393,6 @@
       <c r="O174" t="n">
         <v>18</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="S174" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35041,9 +34783,6 @@
       <c r="O176" t="n">
         <v>32</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="S176" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35434,9 +35173,6 @@
       <c r="O178" t="n">
         <v>33</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35827,9 +35563,6 @@
       <c r="O180" t="n">
         <v>33</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36220,9 +35953,6 @@
       <c r="O182" t="n">
         <v>47</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36613,9 +36343,6 @@
       <c r="O184" t="n">
         <v>21</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37006,9 +36733,6 @@
       <c r="O186" t="n">
         <v>42</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="S186" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37399,9 +37123,6 @@
       <c r="O188" t="n">
         <v>23</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="S188" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37792,9 +37513,6 @@
       <c r="O190" t="n">
         <v>40</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38185,9 +37903,6 @@
       <c r="O192" t="n">
         <v>19</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="S192" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38578,9 +38293,6 @@
       <c r="O194" t="n">
         <v>33</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="S194" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38971,9 +38683,6 @@
       <c r="O196" t="n">
         <v>20</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="S196" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39842,9 +39551,6 @@
       <c r="O200" t="n">
         <v>25</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40235,9 +39941,6 @@
       <c r="O202" t="n">
         <v>32</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40867,9 +40570,6 @@
       <c r="O205" t="n">
         <v>40</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41260,9 +40960,6 @@
       <c r="O207" t="n">
         <v>22</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41892,9 +41589,6 @@
       <c r="O210" t="n">
         <v>28</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="S210" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42285,9 +41979,6 @@
       <c r="O212" t="n">
         <v>23</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="S212" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42917,9 +42608,6 @@
       <c r="O215" t="n">
         <v>41</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="S215" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43310,9 +42998,6 @@
       <c r="O217" t="n">
         <v>34</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="S217" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43942,9 +43627,6 @@
       <c r="O220" t="n">
         <v>27</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44335,9 +44017,6 @@
       <c r="O222" t="n">
         <v>21</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="S222" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44967,9 +44646,6 @@
       <c r="O225" t="n">
         <v>39</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="S225" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45360,9 +45036,6 @@
       <c r="O227" t="n">
         <v>28</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="S227" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45992,9 +45665,6 @@
       <c r="O230" t="n">
         <v>38</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="S230" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46385,9 +46055,6 @@
       <c r="O232" t="n">
         <v>20</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47017,9 +46684,6 @@
       <c r="O235" t="n">
         <v>56</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="S235" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47410,9 +47074,6 @@
       <c r="O237" t="n">
         <v>32</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48042,9 +47703,6 @@
       <c r="O240" t="n">
         <v>42</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48435,9 +48093,6 @@
       <c r="O242" t="n">
         <v>14</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="S242" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49067,9 +48722,6 @@
       <c r="O245" t="n">
         <v>64</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="S245" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49460,9 +49112,6 @@
       <c r="O247" t="n">
         <v>15</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="S247" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50092,9 +49741,6 @@
       <c r="O250" t="n">
         <v>29</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="S250" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50485,9 +50131,6 @@
       <c r="O252" t="n">
         <v>20</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="S252" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51116,9 +50759,6 @@
       </c>
       <c r="O255" t="n">
         <v>24</v>
-      </c>
-      <c r="Q255" t="n">
-        <v>0</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
